--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,7 +615,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-05</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -889,7 +753,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2022-05-22</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1227,7 +1091,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2022-05-16</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -4641,929 +4505,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>KOKO RESERVE - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>82 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>18 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>29 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>35 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>17&amp;18/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 1965呎 (4+房)
-$5,100万
-$25,954/呎
-(22年-05月)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1788呎 (4+房)
-$4,308万
-$24,094/呎
-(23年-08月)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 1755呎 (4+房)
-$3,565万
-$20,313/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 1992呎 (4+房)
-$5,500万
-$27,610/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 1956呎 (4+房)
-$4,120万
-$21,063/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1172呎 (4+房)
-$2,650万
-$22,611/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-$1,509万
-$19,448/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 897呎 (3房)
-$1,703万
-$18,986/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1172呎 (4+房)
-$2,222万
-$18,959/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-$1,114万
-$22,093/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-$1,149万
-$22,090/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-$1,520万
-$19,582/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 897呎 (3房)
-$1,700万
-$18,952/呎
-(25年-08月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1172呎 (4+房)
-$2,259万
-$19,275/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-$1,515万
-$19,523/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 897呎 (3房)
-$1,693万
-$18,874/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1172呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-$1,546万
-$18,671/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-$982万
-$19,490/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-$1,142万
-$21,962/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-$1,510万
-$19,465/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 897呎 (3房)
-$1,705万
-$19,004/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1175呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-$1,033万
-$19,869/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1175呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-$1,135万
-$21,829/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1175呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-$974万
-$19,315/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-$972万
-$18,683/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1175呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-$1,080万
-$21,419/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-$988万
-$19,010/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1175呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-$986万
-$18,954/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>E | 765呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1175呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-$1,073万
-$21,292/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-$983万
-$18,898/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 764呎 (3房)
-$1,436万
-$18,801/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 776呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1175呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 828呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>D | 520呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 737呎 (3房)
-$1,442万
-$19,566/呎
-(25年-08月)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 733呎 (3房)
-$1,472万
-$20,078/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1171呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr"/>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 504呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>D | 525呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr"/>
-      <c r="H18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 1122呎 (4+房)
-$2,240万
-$19,964/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr"/>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 482呎 (2房)
-$953万
-$19,772/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 503呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr"/>
-      <c r="H19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>1&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr"/>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1687呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr"/>
-      <c r="E20" s="17" t="inlineStr"/>
-      <c r="F20" s="17" t="inlineStr"/>
-      <c r="G20" s="17" t="inlineStr"/>
-      <c r="H20" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4505,4 +4684,929 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>17&amp;18</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 1965呎 (4+房)
+$5100万
+$25,954/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1788呎 (4+房)
+$4308万
+$24,094/呎
+(23年-08月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1755呎 (4+房)
+$3565万
+$20,313/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 1992呎 (4+房)
+$5500万
+$27,610/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 1956呎 (4+房)
+$4120万
+$21,063/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1172呎 (4+房)
+$2650万
+$22,611/呎
+(22年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+$1509万
+$19,448/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 897呎 (3房)
+$1703万
+$18,986/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1172呎 (4+房)
+$2222万
+$18,959/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+$1114万
+$22,093/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+$1149万
+$22,090/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+$1520万
+$19,582/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 897呎 (3房)
+$1700万
+$18,952/呎
+(25年-08月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1172呎 (4+房)
+$2259万
+$19,275/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+$1515万
+$19,523/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 897呎 (3房)
+$1693万
+$18,874/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1172呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+$1546万
+$18,671/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+$982万
+$19,490/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+$1142万
+$21,962/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+$1510万
+$19,465/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 897呎 (3房)
+$1705万
+$19,004/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1175呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+$1033万
+$19,869/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1175呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+$1135万
+$21,829/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1175呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+$974万
+$19,315/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+$972万
+$18,683/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1175呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+$1080万
+$21,419/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+$988万
+$19,010/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1175呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+$986万
+$18,954/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 765呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1175呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+$1073万
+$21,292/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+$983万
+$18,898/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 764呎 (3房)
+$1436万
+$18,801/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 776呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1175呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 828呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 520呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 737呎 (3房)
+$1442万
+$19,566/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 733呎 (3房)
+$1472万
+$20,078/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1171呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr"/>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 504呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 525呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr"/>
+      <c r="H17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 1122呎 (4+房)
+$2240万
+$19,964/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 482呎 (2房)
+$953万
+$19,772/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 503呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr"/>
+      <c r="H18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr"/>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1687呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr"/>
+      <c r="F19" s="21" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr"/>
+      <c r="H19" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -759,6 +783,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>41200000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>21063</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -805,6 +845,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>27610</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -851,6 +907,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>35650000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>20313</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -897,6 +969,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>43080000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>24094</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -943,6 +1031,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>51000000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>25954</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -989,6 +1093,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>17030000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>18986</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1035,6 +1155,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>15092000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>19448</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1085,6 +1221,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1135,6 +1291,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1185,6 +1361,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1235,6 +1431,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1281,6 +1497,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>26500000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>22611</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1327,6 +1559,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>18952</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1373,6 +1621,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>15196000</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>19582</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1423,6 +1687,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1469,6 +1753,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>10424452</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>20047</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1515,6 +1815,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>10105012</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>20050</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1565,6 +1881,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1611,6 +1947,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>22220000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>18959</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1657,6 +2009,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>16930000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>18874</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1703,6 +2071,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>15150000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>19523</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1753,6 +2137,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1803,6 +2207,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1853,6 +2277,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -1903,6 +2347,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1949,6 +2413,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>22590000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>19275</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1995,6 +2475,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>17047000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>19004</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2041,6 +2537,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>15105000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>19465</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2091,6 +2603,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2137,6 +2669,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>10363650</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>19930</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2183,6 +2731,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>9823000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>19490</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2229,6 +2793,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>15460000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>18671</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2279,6 +2859,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2329,6 +2929,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2379,6 +2999,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2425,6 +3065,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>10332000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>19869</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2475,6 +3131,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2525,6 +3201,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2575,6 +3271,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2625,6 +3341,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2675,6 +3411,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2721,6 +3477,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>10301032</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>19810</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2771,6 +3543,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2821,6 +3613,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2871,6 +3683,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2921,6 +3753,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2971,6 +3823,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3017,6 +3889,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>9715000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>18683</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3063,6 +3951,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>9735000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>19315</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3113,6 +4017,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3163,6 +4087,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3213,6 +4157,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3263,6 +4227,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3309,6 +4293,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>9885000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>19010</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3355,6 +4355,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>9796462</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>19437</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3405,6 +4421,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3455,6 +4491,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3505,6 +4561,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3555,6 +4631,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3601,6 +4697,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>9856000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>18954</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3651,6 +4763,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -3701,6 +4833,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3751,6 +4903,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3801,6 +4973,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3847,6 +5039,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>14364000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>18801</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3893,6 +5101,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>9827000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>18898</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3939,6 +5163,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>9738382</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>19322</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>120天現金優惠付款計劃</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3989,6 +5229,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4039,6 +5299,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4085,6 +5365,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>14717000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>20078</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4131,6 +5427,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>14420000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>19566</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4181,6 +5493,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4231,6 +5563,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4281,6 +5633,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4331,6 +5703,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4381,6 +5773,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4431,6 +5843,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4481,6 +5913,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4531,6 +5983,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -4577,6 +6049,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>9530000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>19772</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4627,6 +6115,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4673,13 +6181,29 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>22400000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>19964</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4829,7 +6353,7 @@
           <t>A | 1965呎 (4+房)
 $5100万
 $25,954/呎
-(22年-05月)</t>
+(22年-05月-22日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -4837,7 +6361,7 @@
           <t>B | 1788呎 (4+房)
 $4308万
 $24,094/呎
-(23年-08月)</t>
+(23年-08月-23日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -4845,7 +6369,7 @@
           <t>C | 1755呎 (4+房)
 $3565万
 $20,313/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -4854,7 +6378,7 @@
           <t>E | 1992呎 (4+房)
 $5500万
 $27,610/呎
-(22年-05月)</t>
+(22年-05月-05日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr"/>
@@ -4863,7 +6387,7 @@
           <t>G | 1956呎 (4+房)
 $4120万
 $21,063/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -4878,7 +6402,7 @@
           <t>A | 1172呎 (4+房)
 $2650万
 $22,611/呎
-(22年-05月)</t>
+(22年-05月-16日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -4918,7 +6442,7 @@
           <t>F | 776呎 (3房)
 $1509万
 $19,448/呎
-(26年-01月)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -4926,7 +6450,7 @@
           <t>G | 897呎 (3房)
 $1703万
 $18,986/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -4941,7 +6465,7 @@
           <t>A | 1172呎 (4+房)
 $2222万
 $18,959/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -4981,7 +6505,7 @@
           <t>F | 776呎 (3房)
 $1520万
 $19,582/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -4989,7 +6513,7 @@
           <t>G | 897呎 (3房)
 $1700万
 $18,952/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
     </row>
@@ -5004,7 +6528,7 @@
           <t>A | 1172呎 (4+房)
 $2259万
 $19,275/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -5044,7 +6568,7 @@
           <t>F | 776呎 (3房)
 $1515万
 $19,523/呎
-(26年-06月)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -5052,7 +6576,7 @@
           <t>G | 897呎 (3房)
 $1693万
 $18,874/呎
-(25年-12月)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -5075,7 +6599,7 @@
           <t>B | 828呎 (3房)
 $1546万
 $18,671/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -5083,7 +6607,7 @@
           <t>C | 504呎 (2房)
 $982万
 $19,490/呎
-(26年-06月)</t>
+(26年-06月-10日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -5107,7 +6631,7 @@
           <t>F | 776呎 (3房)
 $1510万
 $19,465/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -5115,7 +6639,7 @@
           <t>G | 897呎 (3房)
 $1705万
 $19,004/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -5154,7 +6678,7 @@
           <t>D | 520呎 (2房)
 $1033万
 $19,869/呎
-(26年-06月)</t>
+(26年-06月-20日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -5258,7 +6782,7 @@
           <t>C | 504呎 (2房)
 $974万
 $19,315/呎
-(26年-06月)</t>
+(26年-06月-15日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -5266,7 +6790,7 @@
           <t>D | 520呎 (2房)
 $972万
 $18,683/呎
-(25年-09月)</t>
+(25年-09月-08日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -5322,7 +6846,7 @@
           <t>D | 520呎 (2房)
 $988万
 $19,010/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -5378,7 +6902,7 @@
           <t>D | 520呎 (2房)
 $986万
 $18,954/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -5434,7 +6958,7 @@
           <t>D | 520呎 (2房)
 $983万
 $18,898/呎
-(26年-06月)</t>
+(26年-06月-07日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -5442,7 +6966,7 @@
           <t>E | 764呎 (3房)
 $1436万
 $18,801/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -5498,7 +7022,7 @@
           <t>E | 737呎 (3房)
 $1442万
 $19,566/呎
-(25年-08月)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -5506,7 +7030,7 @@
           <t>F | 733呎 (3房)
 $1472万
 $20,078/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr"/>
@@ -5557,7 +7081,7 @@
           <t>A | 1122呎 (4+房)
 $2240万
 $19,964/呎
-(25年-05月)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr"/>
@@ -5566,7 +7090,7 @@
           <t>C | 482呎 (2房)
 $953万
 $19,772/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">

--- a/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
+++ b/files/九龙-茶果岭、油塘及鲤鱼门-KOKO RESERVE.xlsx
@@ -7073,10 +7073,31 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr"/>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1687呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr"/>
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr"/>
+      <c r="H18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 1122呎 (4+房)
 $2240万
@@ -7084,8 +7105,8 @@
 (25年-05月-22日)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 482呎 (2房)
 $953万
@@ -7093,7 +7114,7 @@
 (26年-03月-22日)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 503呎 (2房)
 招标单位
@@ -7101,27 +7122,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr"/>
-      <c r="G18" s="21" t="inlineStr"/>
-      <c r="H18" s="21" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>1&amp;2</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr"/>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 1687呎 (4+房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr"/>
       <c r="F19" s="21" t="inlineStr"/>
       <c r="G19" s="21" t="inlineStr"/>
       <c r="H19" s="21" t="inlineStr"/>
